--- a/currentbuild/StructureDefinition-no-domain-Trustframework-Location-EncounterPointofcare.xlsx
+++ b/currentbuild/StructureDefinition-no-domain-Trustframework-Location-EncounterPointofcare.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:22:30+00:00</t>
+    <t>2024-06-11T05:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
